--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Escritorio\Documents\GitHub\TPI-Programaci-n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6211560-11E1-4DBD-BB31-BD79251C05B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C38E7-BDB4-41B9-9DA6-2D66A43BF1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C63C7B8C-6C6C-4C5C-95A6-61AF7ED59A05}"/>
+    <workbookView xWindow="-20610" yWindow="1965" windowWidth="20730" windowHeight="11160" xr2:uid="{C63C7B8C-6C6C-4C5C-95A6-61AF7ED59A05}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>Orden de trabajo</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dario </t>
+  </si>
+  <si>
+    <t>En curso</t>
   </si>
 </sst>
 </file>
@@ -548,7 +551,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -572,8 +575,12 @@
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -582,8 +589,12 @@
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1">

--- a/Cronograma.xlsx
+++ b/Cronograma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Escritorio\Documents\GitHub\TPI-Programaci-n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635C38E7-BDB4-41B9-9DA6-2D66A43BF1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5920AD7E-0125-4965-BDC2-C7EA47664624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="1965" windowWidth="20730" windowHeight="11160" xr2:uid="{C63C7B8C-6C6C-4C5C-95A6-61AF7ED59A05}"/>
   </bookViews>
@@ -565,7 +565,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -579,7 +579,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
